--- a/data/The-Cancer-Genomic-Atlas/2023-06-29_clean/study-manifest.xlsx
+++ b/data/The-Cancer-Genomic-Atlas/2023-06-29_clean/study-manifest.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10611"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10917"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mjohnson/Projects/SDD-Dataset/data/The-Cancer-Genomic-Atlas/2023-06-29_clean/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AB6230C-B6B4-D94B-834A-AFC7AECC1FCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D171B31D-6E76-2B49-A3F1-1A9ECB48A264}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="26440" yWindow="3140" windowWidth="23480" windowHeight="28420" activeTab="1" xr2:uid="{F95621CE-DA22-264D-8ECD-5BC9EF74B4B8}"/>
+    <workbookView xWindow="9280" yWindow="800" windowWidth="23480" windowHeight="19700" xr2:uid="{F95621CE-DA22-264D-8ECD-5BC9EF74B4B8}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="corrections" sheetId="2" r:id="rId2"/>
+    <sheet name="prefix" sheetId="3" r:id="rId2"/>
+    <sheet name="corrections" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="139">
   <si>
     <t>Project Number</t>
   </si>
@@ -130,13 +131,349 @@
   </si>
   <si>
     <t>Add type</t>
+  </si>
+  <si>
+    <t>PH</t>
+  </si>
+  <si>
+    <t>Data</t>
+  </si>
+  <si>
+    <t>clinicalTenRows.xlsx</t>
+  </si>
+  <si>
+    <t>Prefix</t>
+  </si>
+  <si>
+    <t>URI</t>
+  </si>
+  <si>
+    <t>chebi</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/CHEBI_</t>
+  </si>
+  <si>
+    <t>cmo</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/CMO_</t>
+  </si>
+  <si>
+    <t>cogat</t>
+  </si>
+  <si>
+    <t>http://www.cognitiveatlas.org/ontology/cogat.owl#CAO_</t>
+  </si>
+  <si>
+    <t>doid</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/DOID_</t>
+  </si>
+  <si>
+    <t>efo</t>
+  </si>
+  <si>
+    <t>http://www.ebi.ac.uk/efo/EFO_</t>
+  </si>
+  <si>
+    <t>envo</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/ENVO_</t>
+  </si>
+  <si>
+    <t>exo</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/ExO_</t>
+  </si>
+  <si>
+    <t>fma</t>
+  </si>
+  <si>
+    <t>http://purl.org/sig/ont/fma/fma</t>
+  </si>
+  <si>
+    <t>hasco</t>
+  </si>
+  <si>
+    <t>http://hadatac.org/ont/hasco/</t>
+  </si>
+  <si>
+    <t>hhear</t>
+  </si>
+  <si>
+    <t>http://purl.org/twc/HHEAR_</t>
+  </si>
+  <si>
+    <t>hp</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/HP_</t>
+  </si>
+  <si>
+    <t>maxo</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/MAXO_</t>
+  </si>
+  <si>
+    <t>ncit</t>
+  </si>
+  <si>
+    <t>http://ncicb.nci.nih.gov/xml/owl/EVS/Thesaurus.owl#</t>
+  </si>
+  <si>
+    <t>nhanes</t>
+  </si>
+  <si>
+    <t>http://purl.org/twc/NHANES_</t>
+  </si>
+  <si>
+    <t>obo</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/</t>
+  </si>
+  <si>
+    <t>pato</t>
+  </si>
+  <si>
+    <r>
+      <t>http://purl.obolibrary.org/obo/</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>PATO_</t>
+    </r>
+  </si>
+  <si>
+    <t>prov</t>
+  </si>
+  <si>
+    <t>http://www.w3.org/ns/prov#</t>
+  </si>
+  <si>
+    <t>pubchem</t>
+  </si>
+  <si>
+    <t>https://pubchem.ncbi.nlm.nih.gov/</t>
+  </si>
+  <si>
+    <t>sio</t>
+  </si>
+  <si>
+    <t>http://semanticscience.org/resource/</t>
+  </si>
+  <si>
+    <t>snomedct</t>
+  </si>
+  <si>
+    <t>http://purl.bioontology.org/ontology/SNOMEDCT/</t>
+  </si>
+  <si>
+    <t>stato</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/STATO_</t>
+  </si>
+  <si>
+    <t>time</t>
+  </si>
+  <si>
+    <t>http://www.w3.org/2006/time#</t>
+  </si>
+  <si>
+    <t>uberon</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/UBERON_</t>
+  </si>
+  <si>
+    <t>uo</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/UO_</t>
+  </si>
+  <si>
+    <t>oae</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/OAE_</t>
+  </si>
+  <si>
+    <t>sio:Identifier</t>
+  </si>
+  <si>
+    <t>sio:SIO_000115</t>
+  </si>
+  <si>
+    <t>sio:BiologicalSex</t>
+  </si>
+  <si>
+    <t>sio:SIO_010029</t>
+  </si>
+  <si>
+    <t>sio:Race</t>
+  </si>
+  <si>
+    <t>sio:SIO_001015</t>
+  </si>
+  <si>
+    <t>sio:Ethnicity</t>
+  </si>
+  <si>
+    <t>sio:SIO_001014</t>
+  </si>
+  <si>
+    <t>sio:Age</t>
+  </si>
+  <si>
+    <t>sio:SIO_001013</t>
+  </si>
+  <si>
+    <t>sio:TimeInterval</t>
+  </si>
+  <si>
+    <t>sio:SIO_000417</t>
+  </si>
+  <si>
+    <t>sio:LifeStatus</t>
+  </si>
+  <si>
+    <t>sio:SIO_010057</t>
+  </si>
+  <si>
+    <t>sio:TimeInstant</t>
+  </si>
+  <si>
+    <t>sio:SIO_000418</t>
+  </si>
+  <si>
+    <t>sio:ExperimentalProtocol</t>
+  </si>
+  <si>
+    <t>sio:SIO_001043</t>
+  </si>
+  <si>
+    <t>sio:Disease</t>
+  </si>
+  <si>
+    <t>sio:SIO_010299</t>
+  </si>
+  <si>
+    <t>sio:Site</t>
+  </si>
+  <si>
+    <t>sio:SIO_000019</t>
+  </si>
+  <si>
+    <t>sio:SpatialRegion</t>
+  </si>
+  <si>
+    <t>sio:SIO_000370</t>
+  </si>
+  <si>
+    <t>sio:Comment</t>
+  </si>
+  <si>
+    <t>sio:SIO_001167</t>
+  </si>
+  <si>
+    <t>sio:Day</t>
+  </si>
+  <si>
+    <t>sio:SIO_000430</t>
+  </si>
+  <si>
+    <t>sio:Year</t>
+  </si>
+  <si>
+    <t>sio:SIO_000428</t>
+  </si>
+  <si>
+    <t>sio:Human</t>
+  </si>
+  <si>
+    <t>sio:SIO_000485</t>
+  </si>
+  <si>
+    <t>sio:SubjectRole</t>
+  </si>
+  <si>
+    <t>sio:SIO_000883</t>
+  </si>
+  <si>
+    <t>sio:Diagnosis</t>
+  </si>
+  <si>
+    <t>sio:SIO_001331</t>
+  </si>
+  <si>
+    <t>sio:isPartOf</t>
+  </si>
+  <si>
+    <t>sio:SIO_000068</t>
+  </si>
+  <si>
+    <t>sio:Coordinate</t>
+  </si>
+  <si>
+    <t>sio:SIO_000071</t>
+  </si>
+  <si>
+    <t>sio:Count</t>
+  </si>
+  <si>
+    <t>sio:SIO_000794</t>
+  </si>
+  <si>
+    <t>sio:Mean</t>
+  </si>
+  <si>
+    <t>sio:SIO_001109</t>
+  </si>
+  <si>
+    <t>sio:Sample</t>
+  </si>
+  <si>
+    <t>sio:SIO_001050</t>
+  </si>
+  <si>
+    <t>CNVTenRows.xlsx</t>
+  </si>
+  <si>
+    <t>sio:Symbol</t>
+  </si>
+  <si>
+    <t>sio:SIO_000105</t>
+  </si>
+  <si>
+    <t>go</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/GO_</t>
+  </si>
+  <si>
+    <t>methylationTenRows.xlsx</t>
+  </si>
+  <si>
+    <t>EXP_miRNATenRows.xlsx</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -158,16 +495,55 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color indexed="8"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="9"/>
+        <bgColor auto="1"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -175,16 +551,42 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFAAAAAA"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFAAAAAA"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFAAAAAA"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFAAAAAA"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -497,7 +899,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96B6D891-895C-3745-8EB8-5887ED002820}">
-  <dimension ref="A1:G122"/>
+  <dimension ref="A1:G123"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="21.1640625" bestFit="1" customWidth="1"/>
@@ -531,7 +933,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -539,14 +941,7 @@
         <v>9</v>
       </c>
       <c r="D2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1">
-        <v>45106</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
@@ -557,196 +952,328 @@
         <v>9</v>
       </c>
       <c r="D3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E3" t="s">
-        <v>16</v>
-      </c>
-      <c r="F3" s="1"/>
+        <v>15</v>
+      </c>
+      <c r="F3" s="1">
+        <v>44479</v>
+      </c>
       <c r="G3" s="1">
         <v>45106</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E4" t="s">
-        <v>17</v>
-      </c>
-      <c r="F4" s="1"/>
+        <v>16</v>
+      </c>
+      <c r="F4" s="1">
+        <v>44479</v>
+      </c>
       <c r="G4" s="1">
         <v>45106</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D5" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="E5" t="s">
-        <v>18</v>
-      </c>
-      <c r="F5" s="1"/>
+        <v>33</v>
+      </c>
+      <c r="F5" s="1">
+        <v>44479</v>
+      </c>
       <c r="G5" s="1">
-        <v>45106</v>
+        <v>45194</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s">
-        <v>11</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="C6" s="2"/>
       <c r="D6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E6" t="s">
-        <v>19</v>
-      </c>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1">
-        <v>45106</v>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D7" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E7" t="s">
-        <v>20</v>
+        <v>17</v>
+      </c>
+      <c r="F7" s="1">
+        <v>44479</v>
       </c>
       <c r="G7" s="1">
-        <v>45106</v>
+        <v>45194</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D8" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E8" t="s">
-        <v>21</v>
+        <v>18</v>
+      </c>
+      <c r="F8" s="1">
+        <v>44479</v>
       </c>
       <c r="G8" s="1">
-        <v>45106</v>
+        <v>45194</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D9" t="s">
+        <v>32</v>
+      </c>
+      <c r="E9" t="s">
+        <v>132</v>
+      </c>
+      <c r="F9" s="1">
+        <v>44479</v>
+      </c>
+      <c r="G9" s="1">
+        <v>45194</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C10" s="2"/>
+      <c r="D10" t="s">
+        <v>31</v>
+      </c>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D11" t="s">
+        <v>6</v>
+      </c>
+      <c r="E11" t="s">
+        <v>19</v>
+      </c>
+      <c r="F11" s="1">
+        <v>44479</v>
+      </c>
+      <c r="G11" s="1">
+        <v>45194</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>11</v>
+      </c>
+      <c r="D12" t="s">
+        <v>5</v>
+      </c>
+      <c r="E12" t="s">
+        <v>20</v>
+      </c>
+      <c r="F12" s="1">
+        <v>44479</v>
+      </c>
+      <c r="G12" s="1">
+        <v>45194</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13" t="s">
+        <v>11</v>
+      </c>
+      <c r="D13" t="s">
+        <v>32</v>
+      </c>
+      <c r="E13" t="s">
+        <v>137</v>
+      </c>
+      <c r="F13" s="1">
+        <v>44479</v>
+      </c>
+      <c r="G13" s="1">
+        <v>45194</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
         <v>12</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B14" t="s">
         <v>12</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D14" t="s">
+        <v>31</v>
+      </c>
+      <c r="G14" s="1"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>12</v>
+      </c>
+      <c r="B15" t="s">
+        <v>12</v>
+      </c>
+      <c r="D15" t="s">
+        <v>6</v>
+      </c>
+      <c r="E15" t="s">
+        <v>21</v>
+      </c>
+      <c r="F15" s="1">
+        <v>44479</v>
+      </c>
+      <c r="G15" s="1">
+        <v>45194</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>12</v>
+      </c>
+      <c r="B16" t="s">
+        <v>12</v>
+      </c>
+      <c r="D16" t="s">
         <v>5</v>
       </c>
-      <c r="E9" t="s">
+      <c r="E16" t="s">
         <v>22</v>
       </c>
-      <c r="G9" s="1">
-        <v>45106</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="G10" s="1"/>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="G11" s="1"/>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="G12" s="1"/>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="G13" s="1"/>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="G14" s="1"/>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="F15" s="1"/>
-      <c r="G15" s="1"/>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="F16" s="1"/>
-      <c r="G16" s="1"/>
-    </row>
-    <row r="17" spans="6:7" x14ac:dyDescent="0.2">
-      <c r="G17" s="1"/>
-    </row>
-    <row r="18" spans="6:7" x14ac:dyDescent="0.2">
-      <c r="F18" s="1"/>
+      <c r="F16" s="1">
+        <v>44479</v>
+      </c>
+      <c r="G16" s="1">
+        <v>45194</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>12</v>
+      </c>
+      <c r="B17" t="s">
+        <v>12</v>
+      </c>
+      <c r="D17" t="s">
+        <v>32</v>
+      </c>
+      <c r="E17" t="s">
+        <v>138</v>
+      </c>
+      <c r="F17" s="1">
+        <v>44479</v>
+      </c>
+      <c r="G17" s="1">
+        <v>45194</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="G18" s="1"/>
     </row>
-    <row r="19" spans="6:7" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="F19" s="1"/>
       <c r="G19" s="1"/>
     </row>
-    <row r="20" spans="6:7" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="F20" s="1"/>
       <c r="G20" s="1"/>
     </row>
-    <row r="21" spans="6:7" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="G21" s="1"/>
     </row>
-    <row r="22" spans="6:7" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="G22" s="1"/>
     </row>
-    <row r="23" spans="6:7" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="G23" s="1"/>
     </row>
-    <row r="24" spans="6:7" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="G24" s="1"/>
     </row>
-    <row r="25" spans="6:7" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="G25" s="1"/>
     </row>
-    <row r="26" spans="6:7" x14ac:dyDescent="0.2">
-      <c r="F26" s="1"/>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="G26" s="1"/>
     </row>
-    <row r="27" spans="6:7" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="F27" s="1"/>
       <c r="G27" s="1"/>
     </row>
-    <row r="28" spans="6:7" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="F28" s="1"/>
       <c r="G28" s="1"/>
     </row>
-    <row r="29" spans="6:7" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="G29" s="1"/>
     </row>
-    <row r="30" spans="6:7" x14ac:dyDescent="0.2">
-      <c r="F30" s="1"/>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="G30" s="1"/>
     </row>
-    <row r="31" spans="6:7" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="F31" s="1"/>
       <c r="G31" s="1"/>
     </row>
-    <row r="32" spans="6:7" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="F32" s="1"/>
       <c r="G32" s="1"/>
     </row>
@@ -787,10 +1314,10 @@
       <c r="G41" s="1"/>
     </row>
     <row r="42" spans="6:7" x14ac:dyDescent="0.2">
+      <c r="F42" s="1"/>
       <c r="G42" s="1"/>
     </row>
     <row r="43" spans="6:7" x14ac:dyDescent="0.2">
-      <c r="F43" s="1"/>
       <c r="G43" s="1"/>
     </row>
     <row r="44" spans="6:7" x14ac:dyDescent="0.2">
@@ -842,6 +1369,7 @@
       <c r="G55" s="1"/>
     </row>
     <row r="56" spans="6:7" x14ac:dyDescent="0.2">
+      <c r="F56" s="1"/>
       <c r="G56" s="1"/>
     </row>
     <row r="57" spans="6:7" x14ac:dyDescent="0.2">
@@ -863,7 +1391,6 @@
       <c r="G62" s="1"/>
     </row>
     <row r="63" spans="6:7" x14ac:dyDescent="0.2">
-      <c r="F63" s="1"/>
       <c r="G63" s="1"/>
     </row>
     <row r="64" spans="6:7" x14ac:dyDescent="0.2">
@@ -875,13 +1402,13 @@
       <c r="G65" s="1"/>
     </row>
     <row r="66" spans="6:7" x14ac:dyDescent="0.2">
+      <c r="F66" s="1"/>
       <c r="G66" s="1"/>
     </row>
     <row r="67" spans="6:7" x14ac:dyDescent="0.2">
       <c r="G67" s="1"/>
     </row>
     <row r="68" spans="6:7" x14ac:dyDescent="0.2">
-      <c r="F68" s="1"/>
       <c r="G68" s="1"/>
     </row>
     <row r="69" spans="6:7" x14ac:dyDescent="0.2">
@@ -889,10 +1416,10 @@
       <c r="G69" s="1"/>
     </row>
     <row r="70" spans="6:7" x14ac:dyDescent="0.2">
+      <c r="F70" s="1"/>
       <c r="G70" s="1"/>
     </row>
     <row r="71" spans="6:7" x14ac:dyDescent="0.2">
-      <c r="F71" s="1"/>
       <c r="G71" s="1"/>
     </row>
     <row r="72" spans="6:7" x14ac:dyDescent="0.2">
@@ -912,10 +1439,10 @@
       <c r="G75" s="1"/>
     </row>
     <row r="76" spans="6:7" x14ac:dyDescent="0.2">
+      <c r="F76" s="1"/>
       <c r="G76" s="1"/>
     </row>
     <row r="77" spans="6:7" x14ac:dyDescent="0.2">
-      <c r="F77" s="1"/>
       <c r="G77" s="1"/>
     </row>
     <row r="78" spans="6:7" x14ac:dyDescent="0.2">
@@ -923,10 +1450,10 @@
       <c r="G78" s="1"/>
     </row>
     <row r="79" spans="6:7" x14ac:dyDescent="0.2">
+      <c r="F79" s="1"/>
       <c r="G79" s="1"/>
     </row>
     <row r="80" spans="6:7" x14ac:dyDescent="0.2">
-      <c r="F80" s="1"/>
       <c r="G80" s="1"/>
     </row>
     <row r="81" spans="6:7" x14ac:dyDescent="0.2">
@@ -962,10 +1489,10 @@
       <c r="G88" s="1"/>
     </row>
     <row r="89" spans="6:7" x14ac:dyDescent="0.2">
+      <c r="F89" s="1"/>
       <c r="G89" s="1"/>
     </row>
     <row r="90" spans="6:7" x14ac:dyDescent="0.2">
-      <c r="F90" s="1"/>
       <c r="G90" s="1"/>
     </row>
     <row r="91" spans="6:7" x14ac:dyDescent="0.2">
@@ -997,10 +1524,10 @@
       <c r="G97" s="1"/>
     </row>
     <row r="98" spans="6:7" x14ac:dyDescent="0.2">
+      <c r="F98" s="1"/>
       <c r="G98" s="1"/>
     </row>
     <row r="99" spans="6:7" x14ac:dyDescent="0.2">
-      <c r="F99" s="1"/>
       <c r="G99" s="1"/>
     </row>
     <row r="100" spans="6:7" x14ac:dyDescent="0.2">
@@ -1008,10 +1535,10 @@
       <c r="G100" s="1"/>
     </row>
     <row r="101" spans="6:7" x14ac:dyDescent="0.2">
+      <c r="F101" s="1"/>
       <c r="G101" s="1"/>
     </row>
     <row r="102" spans="6:7" x14ac:dyDescent="0.2">
-      <c r="F102" s="1"/>
       <c r="G102" s="1"/>
     </row>
     <row r="103" spans="6:7" x14ac:dyDescent="0.2">
@@ -1019,6 +1546,7 @@
       <c r="G103" s="1"/>
     </row>
     <row r="104" spans="6:7" x14ac:dyDescent="0.2">
+      <c r="F104" s="1"/>
       <c r="G104" s="1"/>
     </row>
     <row r="105" spans="6:7" x14ac:dyDescent="0.2">
@@ -1074,6 +1602,9 @@
     </row>
     <row r="122" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G122" s="1"/>
+    </row>
+    <row r="123" spans="7:7" x14ac:dyDescent="0.2">
+      <c r="G123" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -1082,8 +1613,404 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26FFCCB2-64B9-D242-81DE-8A5DA11AFF5A}">
+  <dimension ref="A1:J27"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="9" max="9" width="14.83203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="I2" t="s">
+        <v>86</v>
+      </c>
+      <c r="J2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A3" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B3" t="s">
+        <v>39</v>
+      </c>
+      <c r="H3" s="4"/>
+      <c r="I3" t="s">
+        <v>88</v>
+      </c>
+      <c r="J3" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A4" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="I4" t="s">
+        <v>90</v>
+      </c>
+      <c r="J4" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A5" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="I5" t="s">
+        <v>92</v>
+      </c>
+      <c r="J5" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A6" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="I6" t="s">
+        <v>94</v>
+      </c>
+      <c r="J6" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="17" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="I7" t="s">
+        <v>96</v>
+      </c>
+      <c r="J7" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A8" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="I8" t="s">
+        <v>98</v>
+      </c>
+      <c r="J8" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A9" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="I9" t="s">
+        <v>100</v>
+      </c>
+      <c r="J9" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A10" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="I10" t="s">
+        <v>102</v>
+      </c>
+      <c r="J10" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A11" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="I11" t="s">
+        <v>104</v>
+      </c>
+      <c r="J11" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A12" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="I12" t="s">
+        <v>106</v>
+      </c>
+      <c r="J12" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A13" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="I13" t="s">
+        <v>108</v>
+      </c>
+      <c r="J13" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A14" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="I14" t="s">
+        <v>110</v>
+      </c>
+      <c r="J14" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A15" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="B15" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="I15" t="s">
+        <v>112</v>
+      </c>
+      <c r="J15" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A16" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="I16" t="s">
+        <v>114</v>
+      </c>
+      <c r="J16" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A17" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="I17" t="s">
+        <v>116</v>
+      </c>
+      <c r="J17" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A18" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="I18" t="s">
+        <v>118</v>
+      </c>
+      <c r="J18" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A19" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="I19" t="s">
+        <v>120</v>
+      </c>
+      <c r="J19" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A20" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="I20" t="s">
+        <v>122</v>
+      </c>
+      <c r="J20" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A21" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="I21" t="s">
+        <v>124</v>
+      </c>
+      <c r="J21" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A22" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="I22" t="s">
+        <v>126</v>
+      </c>
+      <c r="J22" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A23" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="I23" t="s">
+        <v>128</v>
+      </c>
+      <c r="J23" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A24" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="B24" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="I24" t="s">
+        <v>130</v>
+      </c>
+      <c r="J24" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A25" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="I25" t="s">
+        <v>133</v>
+      </c>
+      <c r="J25" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A26" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A27" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="B27" t="s">
+        <v>136</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B10" r:id="rId1" xr:uid="{21FBE708-5FD4-414E-A0A0-32691208E063}"/>
+    <hyperlink ref="B20" r:id="rId2" xr:uid="{AB6173FA-B27E-364B-AAD0-0EA76C3FD7EC}"/>
+    <hyperlink ref="B11" r:id="rId3" xr:uid="{49D2825D-940D-104C-AC86-86CE716C0C4B}"/>
+    <hyperlink ref="B6" r:id="rId4" xr:uid="{9348CCDB-3E33-DF46-8FF4-328C0A0FACD7}"/>
+    <hyperlink ref="B16" r:id="rId5" xr:uid="{013182FB-1506-1D4C-AFFC-866DEF49865C}"/>
+    <hyperlink ref="B14" r:id="rId6" xr:uid="{C571648F-ADFB-324D-B236-6A5E52F2F80F}"/>
+    <hyperlink ref="B25" r:id="rId7" xr:uid="{9C89F8A3-8B9A-5D44-ABCE-BDD48DB18AE4}"/>
+    <hyperlink ref="B8" r:id="rId8" xr:uid="{8D271143-3A4A-8B4B-9732-229411EA8B09}"/>
+    <hyperlink ref="B5" r:id="rId9" xr:uid="{A1F6CCD4-6CA7-8D4A-B558-C44CD776A6CB}"/>
+    <hyperlink ref="B18" r:id="rId10" xr:uid="{B07A7D46-7A3B-B74C-A957-C2C458C4FE50}"/>
+    <hyperlink ref="B4" r:id="rId11" location="CAO_" xr:uid="{58204D88-1F16-4742-BCA5-B0422C165EAC}"/>
+    <hyperlink ref="B22" r:id="rId12" xr:uid="{B6EC17CA-8C1E-F64A-A5D9-1EFA8178E15A}"/>
+    <hyperlink ref="B2" r:id="rId13" xr:uid="{D2DBB768-C64D-914F-97E3-EDF77B940457}"/>
+    <hyperlink ref="B24" r:id="rId14" xr:uid="{6E71FD7E-85B9-D24F-BDA0-5F5F7613A567}"/>
+    <hyperlink ref="B19" r:id="rId15" xr:uid="{4751D0C1-6D74-6A42-BC3D-C8D8916A564B}"/>
+    <hyperlink ref="B23" r:id="rId16" xr:uid="{369628AF-536A-F141-B382-ACC629C39E54}"/>
+    <hyperlink ref="B15" r:id="rId17" xr:uid="{6786E7BA-0F18-BB43-A6C1-D9C470B213BB}"/>
+    <hyperlink ref="B21" r:id="rId18" xr:uid="{F04BF4E0-A04D-884D-A6B4-8B1CB6DA5779}"/>
+    <hyperlink ref="B9" r:id="rId19" xr:uid="{F5712966-7FF2-AF48-8239-BFC4F46A2C64}"/>
+    <hyperlink ref="B26" r:id="rId20" xr:uid="{7AD68DC1-5B4B-CA47-BA47-CA5838D7617F}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE8C70C0-C415-0C4E-89DF-B1AA58B21379}">
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18.1640625" bestFit="1" customWidth="1"/>
@@ -1139,6 +2066,111 @@
         <v>30</v>
       </c>
     </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>10</v>
+      </c>
+      <c r="B19" t="s">
+        <v>10</v>
+      </c>
+      <c r="D19" t="s">
+        <v>6</v>
+      </c>
+      <c r="E19" t="s">
+        <v>17</v>
+      </c>
+      <c r="F19" s="1"/>
+      <c r="G19" s="1">
+        <v>45106</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>10</v>
+      </c>
+      <c r="B20" t="s">
+        <v>10</v>
+      </c>
+      <c r="D20" t="s">
+        <v>5</v>
+      </c>
+      <c r="E20" t="s">
+        <v>18</v>
+      </c>
+      <c r="F20" s="1"/>
+      <c r="G20" s="1">
+        <v>45106</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>11</v>
+      </c>
+      <c r="B21" t="s">
+        <v>11</v>
+      </c>
+      <c r="D21" t="s">
+        <v>6</v>
+      </c>
+      <c r="E21" t="s">
+        <v>19</v>
+      </c>
+      <c r="F21" s="1"/>
+      <c r="G21" s="1">
+        <v>45106</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>11</v>
+      </c>
+      <c r="B22" t="s">
+        <v>11</v>
+      </c>
+      <c r="D22" t="s">
+        <v>5</v>
+      </c>
+      <c r="E22" t="s">
+        <v>20</v>
+      </c>
+      <c r="G22" s="1">
+        <v>45106</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>12</v>
+      </c>
+      <c r="B23" t="s">
+        <v>12</v>
+      </c>
+      <c r="D23" t="s">
+        <v>6</v>
+      </c>
+      <c r="E23" t="s">
+        <v>21</v>
+      </c>
+      <c r="G23" s="1">
+        <v>45106</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>12</v>
+      </c>
+      <c r="B24" t="s">
+        <v>12</v>
+      </c>
+      <c r="D24" t="s">
+        <v>5</v>
+      </c>
+      <c r="E24" t="s">
+        <v>22</v>
+      </c>
+      <c r="G24" s="1">
+        <v>45106</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
